--- a/3-IndustrialProcesses/FoodAndBeverage/Dairy/Documents/DairyCheese_V0_rs_qt.xlsx
+++ b/3-IndustrialProcesses/FoodAndBeverage/Dairy/Documents/DairyCheese_V0_rs_qt.xlsx
@@ -539,7 +539,7 @@
     <t xml:space="preserve">Reference targets for the 21 streams of the qt sheet</t>
   </si>
   <si>
-    <t xml:space="preserve">Problem-table results with the dTmin/2 of each stream, given as values to check your own calculation.</t>
+    <t xml:space="preserve">Problem-table results with the dTmin/2 of each stream.</t>
   </si>
   <si>
     <t xml:space="preserve">Quantity</t>

--- a/3-IndustrialProcesses/FoodAndBeverage/Dairy/Documents/DairyCheese_V0_rs_qt.xlsx
+++ b/3-IndustrialProcesses/FoodAndBeverage/Dairy/Documents/DairyCheese_V0_rs_qt.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">t/h</t>
   </si>
   <si>
-    <t xml:space="preserve">IPESE dairy model (Dardor et al., 2024)</t>
+    <t xml:space="preserve">DWSIM dairy model of Bhatnagar, Flórez-Orrego, Boztas and Dardor; Dardor et al. (2024)</t>
   </si>
   <si>
     <t xml:space="preserve">Operating time</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Basis of all tables</t>
   </si>
   <si>
-    <t xml:space="preserve">Data: IPESE dairy model (DWSIM simulation implemented in ROSMOSE), latest MER runs; IETS Task XXIV dairy data set.</t>
+    <t xml:space="preserve">Data: DWSIM dairy model of Bhatnagar, Flórez-Orrego, Boztas and Dardor; Dardor et al. (2024); latest MER runs.</t>
   </si>
   <si>
     <t xml:space="preserve">Evaporator described effect by effect; condensing and boiling streams use dTmin/2 = 2 K, liquid streams 5 K.</t>
